--- a/Понедельник.xlsx
+++ b/Понедельник.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pinchukna\Desktop\Посещаемость\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pinchukna\Documents\Folder\Generator_rep_attendance\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -860,15 +860,15 @@
       <c r="C8" s="5">
         <v>9433307</v>
       </c>
-      <c r="D8" s="3"/>
+      <c r="D8" s="3" t="s">
+        <v>14</v>
+      </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
-      <c r="J8" s="2" t="s">
-        <v>14</v>
-      </c>
+      <c r="J8" s="2"/>
       <c r="K8" s="5"/>
     </row>
     <row r="9" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">

--- a/Понедельник.xlsx
+++ b/Понедельник.xlsx
@@ -14,7 +14,7 @@
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913" refMode="R1C1"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -87,7 +87,7 @@
     <t>Кинетов Жан Бахытович</t>
   </si>
   <si>
-    <t>Абдрахман Хасен Алпамысович</t>
+    <t>Абдрахманов Хасен Алпамысович</t>
   </si>
 </sst>
 </file>
